--- a/doc/7.BOM et PRIX/Commande.xlsx
+++ b/doc/7.BOM et PRIX/Commande.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/7.BOM et PRIX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{6E66962B-18D2-490B-9F19-F155EEEA3D7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{D8518D0D-A751-4F35-8A32-D0690CF54354}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{6E66962B-18D2-490B-9F19-F155EEEA3D7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{058779A0-DD3F-49D3-9631-94ADF8D0261F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{98312F9F-40E5-413F-AE66-108837480640}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{98312F9F-40E5-413F-AE66-108837480640}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="289">
   <si>
     <t>Commande matériel</t>
   </si>
@@ -1006,7 +1006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1057,31 +1057,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <b val="0"/>
@@ -1307,6 +1290,16 @@
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1324,15 +1317,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CAA7E530-63AD-4179-BC3A-0E8280D5219C}" name="Tableau1" displayName="Tableau1" ref="A3:L23" totalsRowShown="0">
   <autoFilter ref="A3:L23" xr:uid="{2BC3944A-AE14-404C-AA2E-C36CFF839557}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{4BE5C377-EBB8-4100-A8F9-77335D046CF7}" name="Designator" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{269971B4-5955-4E05-B650-FCC1414D6245}" name="Value" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{C09119CC-5532-46BC-8DCE-A06AC133B15F}" name="Name" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{7BDBB2CB-ADC8-4625-A04D-2598529317A8}" name="Manufacturer 1" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{07F25103-0A4A-40F0-84E5-C9F9A4EBDF02}" name="Manufacturer Part Number 1" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{4C416872-2B18-4009-A931-F919ED1F2493}" name="Quantity" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{9B9A2C8F-3116-4BA6-AC11-1D5D6CA460F3}" name="Supplier 1" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{E694E44C-B132-4E35-93F2-40ED0C34D1D6}" name="Supplier Part Number 1" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{3ED78F57-1EDF-4765-812E-962DE724D4B8}" name="Doubler N° composant ?" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{4BE5C377-EBB8-4100-A8F9-77335D046CF7}" name="Designator" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{269971B4-5955-4E05-B650-FCC1414D6245}" name="Value" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{C09119CC-5532-46BC-8DCE-A06AC133B15F}" name="Name" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{7BDBB2CB-ADC8-4625-A04D-2598529317A8}" name="Manufacturer 1" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{07F25103-0A4A-40F0-84E5-C9F9A4EBDF02}" name="Manufacturer Part Number 1" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{4C416872-2B18-4009-A931-F919ED1F2493}" name="Quantity" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{9B9A2C8F-3116-4BA6-AC11-1D5D6CA460F3}" name="Supplier 1" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{E694E44C-B132-4E35-93F2-40ED0C34D1D6}" name="Supplier Part Number 1" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{3ED78F57-1EDF-4765-812E-962DE724D4B8}" name="Doubler N° composant ?" dataDxfId="10"/>
     <tableColumn id="10" xr3:uid="{85DD5FAE-457E-43C0-A6A4-AEC9B25EFD10}" name="Commande"/>
     <tableColumn id="11" xr3:uid="{5D570698-EEAE-48E1-8314-3F50B4423590}" name="Reçu "/>
     <tableColumn id="12" xr3:uid="{3F2F3945-0C86-40E9-8CFD-907DA3BCC90B}" name="Monté"/>
@@ -1342,17 +1335,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2340B6BD-ADFD-4FFD-A893-A933206CBFFE}" name="Tableau2" displayName="Tableau2" ref="A26:L77" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2340B6BD-ADFD-4FFD-A893-A933206CBFFE}" name="Tableau2" displayName="Tableau2" ref="A26:L77" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8">
   <autoFilter ref="A26:L77" xr:uid="{48ECF34D-FC8E-497A-9CBE-3766491F63BF}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5A066223-3E2F-4B7D-9188-2C01F592EF43}" name="Designator" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{DE644072-04A5-4AF2-9F46-22200FBCC1B5}" name="Value" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{2E05C98F-6232-41D4-B27C-1BCB1E85C03F}" name="Name" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{06F21637-05CB-4951-B166-D39CA6F7F03B}" name="Manufacturer 1" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{784B0EDD-A2ED-4CFA-BB86-3C66F2A652F5}" name="Manufacturer Part Number 1" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{C38B4BEB-554C-4553-ABB3-1C52C4C9C071}" name="Quantity" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{5CAD642E-0491-4DA8-B5DA-F507459EEF75}" name="Supplier 1" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{F871F135-D9AC-4CCA-8783-6F4801502393}" name="Supplier Part Number 1" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{5A066223-3E2F-4B7D-9188-2C01F592EF43}" name="Designator" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{DE644072-04A5-4AF2-9F46-22200FBCC1B5}" name="Value" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{2E05C98F-6232-41D4-B27C-1BCB1E85C03F}" name="Name" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{06F21637-05CB-4951-B166-D39CA6F7F03B}" name="Manufacturer 1" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{784B0EDD-A2ED-4CFA-BB86-3C66F2A652F5}" name="Manufacturer Part Number 1" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{C38B4BEB-554C-4553-ABB3-1C52C4C9C071}" name="Quantity" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{5CAD642E-0491-4DA8-B5DA-F507459EEF75}" name="Supplier 1" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{F871F135-D9AC-4CCA-8783-6F4801502393}" name="Supplier Part Number 1" dataDxfId="0"/>
     <tableColumn id="9" xr3:uid="{6E836969-AB36-44DE-805C-BD5F3DFD3C86}" name="Doubler N° composant ?"/>
     <tableColumn id="10" xr3:uid="{9BAB9CDC-2064-43A5-AB28-69D2FF203A1A}" name="Commande"/>
     <tableColumn id="11" xr3:uid="{9DB2FAEC-D8CA-4DD2-963A-8E715E633355}" name="Reçu "/>
@@ -1673,12 +1666,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3752,13 +3745,13 @@
       <c r="H68" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="I68" s="15"/>
-      <c r="J68" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="K68" s="9" t="s">
-        <v>282</v>
-      </c>
+      <c r="I68" s="15">
+        <v>6</v>
+      </c>
+      <c r="J68" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="K68" s="19"/>
       <c r="L68" s="1"/>
     </row>
     <row r="69" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
@@ -4045,7 +4038,7 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="A27:H77">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>$A27="not fitted"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/doc/7.BOM et PRIX/Commande.xlsx
+++ b/doc/7.BOM et PRIX/Commande.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/7.BOM et PRIX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{6E66962B-18D2-490B-9F19-F155EEEA3D7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{058779A0-DD3F-49D3-9631-94ADF8D0261F}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{6E66962B-18D2-490B-9F19-F155EEEA3D7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{3C57F712-06D9-4ECA-B38A-E59FD4D097F4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{98312F9F-40E5-413F-AE66-108837480640}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{98312F9F-40E5-413F-AE66-108837480640}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="295">
   <si>
     <t>Commande matériel</t>
   </si>
@@ -902,6 +902,24 @@
   </si>
   <si>
     <t>Ok</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Not implemented</t>
+  </si>
+  <si>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Erreur commande</t>
+  </si>
+  <si>
+    <t>Changemen composant mais nouveu ok</t>
   </si>
 </sst>
 </file>
@@ -930,7 +948,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -946,6 +964,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1006,7 +1036,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1058,6 +1088,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1314,9 +1361,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CAA7E530-63AD-4179-BC3A-0E8280D5219C}" name="Tableau1" displayName="Tableau1" ref="A3:L23" totalsRowShown="0">
-  <autoFilter ref="A3:L23" xr:uid="{2BC3944A-AE14-404C-AA2E-C36CFF839557}"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CAA7E530-63AD-4179-BC3A-0E8280D5219C}" name="Tableau1" displayName="Tableau1" ref="A3:M23" totalsRowShown="0">
+  <autoFilter ref="A3:M23" xr:uid="{2BC3944A-AE14-404C-AA2E-C36CFF839557}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4BE5C377-EBB8-4100-A8F9-77335D046CF7}" name="Designator" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{269971B4-5955-4E05-B650-FCC1414D6245}" name="Value" dataDxfId="17"/>
     <tableColumn id="3" xr3:uid="{C09119CC-5532-46BC-8DCE-A06AC133B15F}" name="Name" dataDxfId="16"/>
@@ -1329,15 +1376,16 @@
     <tableColumn id="10" xr3:uid="{85DD5FAE-457E-43C0-A6A4-AEC9B25EFD10}" name="Commande"/>
     <tableColumn id="11" xr3:uid="{5D570698-EEAE-48E1-8314-3F50B4423590}" name="Reçu "/>
     <tableColumn id="12" xr3:uid="{3F2F3945-0C86-40E9-8CFD-907DA3BCC90B}" name="Monté"/>
+    <tableColumn id="13" xr3:uid="{4F90A494-9F32-4E90-95CC-9A702F25BC1D}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2340B6BD-ADFD-4FFD-A893-A933206CBFFE}" name="Tableau2" displayName="Tableau2" ref="A26:L77" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8">
-  <autoFilter ref="A26:L77" xr:uid="{48ECF34D-FC8E-497A-9CBE-3766491F63BF}"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2340B6BD-ADFD-4FFD-A893-A933206CBFFE}" name="Tableau2" displayName="Tableau2" ref="A26:M77" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8">
+  <autoFilter ref="A26:M77" xr:uid="{48ECF34D-FC8E-497A-9CBE-3766491F63BF}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{5A066223-3E2F-4B7D-9188-2C01F592EF43}" name="Designator" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{DE644072-04A5-4AF2-9F46-22200FBCC1B5}" name="Value" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{2E05C98F-6232-41D4-B27C-1BCB1E85C03F}" name="Name" dataDxfId="5"/>
@@ -1350,6 +1398,7 @@
     <tableColumn id="10" xr3:uid="{9BAB9CDC-2064-43A5-AB28-69D2FF203A1A}" name="Commande"/>
     <tableColumn id="11" xr3:uid="{9DB2FAEC-D8CA-4DD2-963A-8E715E633355}" name="Reçu "/>
     <tableColumn id="12" xr3:uid="{48AC8E4D-1C9F-4698-BD1B-F4B41A338EB4}" name="Monté"/>
+    <tableColumn id="13" xr3:uid="{BDEC5ADF-67E5-4B07-AD87-125CE5CA2D5B}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1652,7 +1701,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EF0698-4CBF-40C5-B3A6-BB59B99484E9}">
-  <dimension ref="A1:L77"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
@@ -1661,11 +1713,13 @@
     <col min="4" max="4" width="26.28515625" customWidth="1"/>
     <col min="5" max="5" width="28.42578125" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="9" width="32.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="32.140625" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" customWidth="1"/>
+    <col min="13" max="13" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1673,7 +1727,7 @@
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>97</v>
       </c>
@@ -1681,7 +1735,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1718,8 +1772,11 @@
       <c r="L3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -1750,8 +1807,11 @@
       <c r="J4" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K4" s="21" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -1780,8 +1840,11 @@
       <c r="J5" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -1810,8 +1873,11 @@
       <c r="J6" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>24</v>
       </c>
@@ -1840,8 +1906,11 @@
       <c r="J7" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>29</v>
       </c>
@@ -1870,8 +1939,11 @@
       <c r="J8" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>33</v>
       </c>
@@ -1900,8 +1972,11 @@
       <c r="J9" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
@@ -1931,7 +2006,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -1960,8 +2035,11 @@
       <c r="J11" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>46</v>
       </c>
@@ -1994,7 +2072,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>50</v>
       </c>
@@ -2021,8 +2099,11 @@
       <c r="J13" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="K13" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>96</v>
       </c>
@@ -2051,8 +2132,11 @@
       <c r="J14" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K14" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>57</v>
       </c>
@@ -2081,8 +2165,11 @@
       <c r="J15" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>61</v>
       </c>
@@ -2117,7 +2204,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>65</v>
       </c>
@@ -2149,7 +2236,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>70</v>
       </c>
@@ -2184,7 +2271,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>74</v>
       </c>
@@ -2215,7 +2302,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>77</v>
       </c>
@@ -2246,7 +2333,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>80</v>
       </c>
@@ -2273,36 +2360,39 @@
       <c r="J21" s="9" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="K21" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="22"/>
+      <c r="C22" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="22">
         <v>1</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="I22" s="7"/>
-      <c r="J22" s="9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I22" s="22"/>
+      <c r="J22" s="23" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>88</v>
       </c>
@@ -2335,12 +2425,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>1</v>
       </c>
@@ -2377,8 +2467,11 @@
       <c r="L26" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="27" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M26" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="27" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>100</v>
       </c>
@@ -2407,10 +2500,12 @@
       <c r="J27" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>285</v>
       </c>
@@ -2439,10 +2534,12 @@
       <c r="J28" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>108</v>
       </c>
@@ -2471,10 +2568,12 @@
       <c r="J29" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>109</v>
       </c>
@@ -2505,10 +2604,12 @@
       <c r="J30" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>116</v>
       </c>
@@ -2539,10 +2640,12 @@
       <c r="J31" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K31" s="1"/>
+      <c r="K31" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>121</v>
       </c>
@@ -2571,10 +2674,12 @@
       <c r="J32" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K32" s="1"/>
+      <c r="K32" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>125</v>
       </c>
@@ -2603,10 +2708,12 @@
       <c r="J33" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="K33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>128</v>
       </c>
@@ -2635,10 +2742,12 @@
       <c r="J34" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>131</v>
       </c>
@@ -2667,10 +2776,12 @@
       <c r="J35" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>134</v>
       </c>
@@ -2699,10 +2810,12 @@
       <c r="J36" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L36" s="1"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>137</v>
       </c>
@@ -2731,10 +2844,12 @@
       <c r="J37" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
         <v>140</v>
       </c>
@@ -2763,10 +2878,12 @@
       <c r="J38" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K38" s="1"/>
+      <c r="K38" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L38" s="1"/>
     </row>
-    <row r="39" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>144</v>
       </c>
@@ -2795,10 +2912,12 @@
       <c r="J39" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K39" s="1"/>
+      <c r="K39" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L39" s="1"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
         <v>147</v>
       </c>
@@ -2827,10 +2946,12 @@
       <c r="J40" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K40" s="1"/>
+      <c r="K40" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L40" s="1"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>150</v>
       </c>
@@ -2857,42 +2978,49 @@
       <c r="J41" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="K41" s="1"/>
+      <c r="K41" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L41" s="1"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+    <row r="42" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="18" t="s">
+      <c r="B42" s="24"/>
+      <c r="C42" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="F42" s="17">
+      <c r="F42" s="24">
         <v>1</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="18" t="s">
+      <c r="H42" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="26">
         <v>2</v>
       </c>
-      <c r="J42" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J42" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="K42" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="L42" s="27"/>
+      <c r="M42" s="23" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>155</v>
       </c>
@@ -2921,10 +3049,12 @@
       <c r="J43" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K43" s="1"/>
+      <c r="K43" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L43" s="1"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>158</v>
       </c>
@@ -2953,10 +3083,12 @@
       <c r="J44" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L44" s="1"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>37</v>
       </c>
@@ -2983,10 +3115,12 @@
       <c r="J45" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K45" s="1"/>
+      <c r="K45" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L45" s="1"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>165</v>
       </c>
@@ -3015,10 +3149,12 @@
       <c r="J46" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K46" s="1"/>
+      <c r="K46" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L46" s="1"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
         <v>169</v>
       </c>
@@ -3048,10 +3184,12 @@
       <c r="J47" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K47" s="1"/>
+      <c r="K47" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L47" s="1"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
         <v>41</v>
       </c>
@@ -3527,7 +3665,9 @@
       <c r="J61" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K61" s="16"/>
+      <c r="K61" s="16" t="s">
+        <v>277</v>
+      </c>
       <c r="L61" s="1"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3625,40 +3765,47 @@
       <c r="J64" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K64" s="1"/>
+      <c r="K64" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L64" s="1"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="17" t="s">
+    <row r="65" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="18" t="s">
+      <c r="B65" s="24"/>
+      <c r="C65" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="D65" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E65" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="F65" s="17">
+      <c r="F65" s="24">
         <v>1</v>
       </c>
-      <c r="G65" s="18" t="s">
+      <c r="G65" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H65" s="18" t="s">
+      <c r="H65" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="I65" s="15"/>
-      <c r="J65" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I65" s="26"/>
+      <c r="J65" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="K65" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="L65" s="27"/>
+      <c r="M65" s="23" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>241</v>
       </c>
@@ -3690,7 +3837,7 @@
       </c>
       <c r="L66" s="1"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>243</v>
       </c>
@@ -3722,7 +3869,7 @@
       </c>
       <c r="L67" s="1"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>245</v>
       </c>
@@ -3751,10 +3898,12 @@
       <c r="J68" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K68" s="19"/>
+      <c r="K68" s="19" t="s">
+        <v>277</v>
+      </c>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>84</v>
       </c>
@@ -3781,10 +3930,12 @@
       <c r="J69" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K69" s="1"/>
+      <c r="K69" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>253</v>
       </c>
@@ -3811,10 +3962,12 @@
       <c r="J70" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K70" s="1"/>
+      <c r="K70" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>255</v>
       </c>
@@ -3846,7 +3999,7 @@
       </c>
       <c r="L71" s="1"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>260</v>
       </c>
@@ -3873,10 +4026,12 @@
       <c r="J72" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K72" s="1"/>
+      <c r="K72" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L72" s="1"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>263</v>
       </c>
@@ -3903,10 +4058,12 @@
       <c r="J73" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K73" s="1"/>
+      <c r="K73" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
         <v>266</v>
       </c>
@@ -3933,10 +4090,12 @@
       <c r="J74" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K74" s="1"/>
+      <c r="K74" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>269</v>
       </c>
@@ -3963,10 +4122,12 @@
       <c r="J75" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="K75" s="1"/>
+      <c r="K75" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
         <v>272</v>
       </c>
@@ -4000,7 +4161,7 @@
       </c>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>275</v>
       </c>
@@ -4042,10 +4203,11 @@
       <formula>$A27="not fitted"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" scale="58" orientation="landscape" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>